--- a/backend/seed_data/day0_import_template.xlsx
+++ b/backend/seed_data/day0_import_template.xlsx
@@ -451,180 +451,180 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Roasted Garlic Mashed Potatoes</t>
+          <t>Aluminum Foil Roll</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PERSCARE-001</t>
+          <t>SKU-DEMO-HOUSEHOLD-001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Personal Care</t>
+          <t>Household Supplies</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.47</v>
+        <v>61.98</v>
       </c>
       <c r="E2" t="n">
-        <v>16.76</v>
+        <v>35.95</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2028-05-15</t>
+          <t>2028-01-03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Wireless Charging Station</t>
+          <t>Sourdough Baguette</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SKU-DEMO-COFFEE-001</t>
+          <t>SKU-DEMO-BAKERY-001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Coffee &amp; Tea</t>
+          <t>Bakery</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>200.08</v>
+        <v>282.32</v>
       </c>
       <c r="E3" t="n">
-        <v>120.05</v>
+        <v>203.27</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2027-08-23</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ice Cream</t>
+          <t>Sliced Turkey Breast 200g</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SKU-DEMO-SNACK-001</t>
+          <t>SKU-DEMO-DELI-001</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Snacks</t>
+          <t>Deli</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>250.47</v>
+        <v>227.49</v>
       </c>
       <c r="E4" t="n">
-        <v>157.8</v>
+        <v>159.24</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2028-02-26</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Personal Safety Alarm</t>
+          <t>Deodorant 150ml</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SKU-DEMO-BEV-001</t>
+          <t>SKU-DEMO-PERSCARE-001</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Personal Care</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>77.42</v>
+        <v>133.59</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>73.47</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2028-07-27</t>
+          <t>2027-09-12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Car Vacuum Cleaner</t>
+          <t>Tomatoes 1kg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SKU-DEMO-DAIRY-001</t>
+          <t>SKU-DEMO-PRODUCE-001</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Produce</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>67.42</v>
+        <v>90.59</v>
       </c>
       <c r="E6" t="n">
-        <v>45.85</v>
+        <v>67.94</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2028-05-31</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DIY Candle Kit</t>
+          <t>Peanut Butter 400g</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SKU-DEMO-FROZEN-001</t>
+          <t>SKU-DEMO-PANTRY-001</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Frozen Food</t>
+          <t>Breakfast &amp; Pantry</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>223.88</v>
+        <v>19.8</v>
       </c>
       <c r="E7" t="n">
-        <v>150</v>
+        <v>12.87</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2028-04-05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Suede Ankle Booties</t>
+          <t>Peanut Butter 400g</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PANTRY-001</t>
+          <t>SKU-DEMO-PANTRY-002</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -633,1034 +633,1034 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>49.34</v>
+        <v>221.41</v>
       </c>
       <c r="E8" t="n">
-        <v>32.07</v>
+        <v>143.92</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2027-09-27</t>
+          <t>2027-08-22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Smartphone Projector</t>
+          <t>Sparkling Water 500ml</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SKU-DEMO-BAKERY-001</t>
+          <t>SKU-DEMO-BEV-001</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bakery</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>96.5</v>
+        <v>115.67</v>
       </c>
       <c r="E9" t="n">
-        <v>69.48</v>
+        <v>71.72</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2027-11-17</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sun-Dried Tomatoes</t>
+          <t>Baby Wipes Pack</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PRODUCE-001</t>
+          <t>SKU-DEMO-BABY-001</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Baby Products</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>101.69</v>
+        <v>27.11</v>
       </c>
       <c r="E10" t="n">
-        <v>76.27</v>
+        <v>16.27</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2028-02-11</t>
+          <t>2028-06-30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gaming Headset</t>
+          <t>Energy Drink 250ml</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PET-001</t>
+          <t>SKU-DEMO-BEV-002</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>60.98</v>
+        <v>164.55</v>
       </c>
       <c r="E11" t="n">
-        <v>36.59</v>
+        <v>102.02</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2028-04-15</t>
+          <t>2027-11-09</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ricotta Cheese</t>
+          <t>Canned Tomatoes 400g</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SKU-DEMO-BAKERY-002</t>
+          <t>SKU-DEMO-CANNED-001</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bakery</t>
+          <t>Canned Goods &amp; Legumes</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.6</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>9.07</v>
+        <v>52.53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2027-11-28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Almond Butter Cups</t>
+          <t>Mixed Nuts 200g</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SKU-DEMO-DELI-001</t>
+          <t>SKU-DEMO-SNACK-001</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Deli</t>
+          <t>Snacks</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>174.35</v>
+        <v>225.46</v>
       </c>
       <c r="E13" t="n">
-        <v>122.04</v>
+        <v>142.04</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2028-04-13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cucumber Lime Sparkling Water</t>
+          <t>Bleach 1L</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SKU-DEMO-FROZEN-002</t>
+          <t>SKU-DEMO-CLEAN-001</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Frozen Food</t>
+          <t>Cleaning Supplies</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>92.81</v>
+        <v>57.68</v>
       </c>
       <c r="E14" t="n">
-        <v>62.18</v>
+        <v>32.88</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2028-03-23</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dog Collar</t>
+          <t>Honey 450g</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SKU-DEMO-DELI-002</t>
+          <t>SKU-DEMO-PANTRY-003</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Deli</t>
+          <t>Breakfast &amp; Pantry</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>286.28</v>
+        <v>128.13</v>
       </c>
       <c r="E15" t="n">
-        <v>200.4</v>
+        <v>83.28</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2028-06-16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Vegetable Korma</t>
+          <t>Pretzels 200g</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SKU-DEMO-HOUSEHOLD-001</t>
+          <t>SKU-DEMO-SNACK-002</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Household Supplies</t>
+          <t>Snacks</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>274.99</v>
+        <v>233.25</v>
       </c>
       <c r="E16" t="n">
-        <v>159.49</v>
+        <v>146.95</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2027-09-19</t>
+          <t>2028-05-10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pet Grooming Scissors</t>
+          <t>Chicken Breast 1kg</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SKU-DEMO-DELI-003</t>
+          <t>SKU-DEMO-MEAT-001</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Deli</t>
+          <t>Meat</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>191.42</v>
+        <v>196.15</v>
       </c>
       <c r="E17" t="n">
-        <v>133.99</v>
+        <v>143.19</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2028-02-16</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rolling Cooler</t>
+          <t>Sliced Turkey Breast 200g</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PANTRY-002</t>
+          <t>SKU-DEMO-DELI-002</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Breakfast &amp; Pantry</t>
+          <t>Deli</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>212.14</v>
+        <v>31.17</v>
       </c>
       <c r="E18" t="n">
-        <v>137.89</v>
+        <v>21.82</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2028-03-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Floral Summer Dress</t>
+          <t>Potato Chips 150g</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SKU-DEMO-DELI-004</t>
+          <t>SKU-DEMO-SNACK-003</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Deli</t>
+          <t>Snacks</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>299.97</v>
+        <v>29.89</v>
       </c>
       <c r="E19" t="n">
-        <v>209.98</v>
+        <v>18.83</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2028-05-23</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Almond Flour Cookies</t>
+          <t>Chicken Breast 1kg</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SKU-DEMO-CANNED-001</t>
+          <t>SKU-DEMO-MEAT-002</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Canned Goods &amp; Legumes</t>
+          <t>Meat</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>82.69</v>
+        <v>229.17</v>
       </c>
       <c r="E20" t="n">
-        <v>53.75</v>
+        <v>167.29</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2028-06-07</t>
+          <t>2027-11-03</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Vacuum Sealer Machine</t>
+          <t>Smoked Salmon 150g</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SKU-DEMO-SNACK-002</t>
+          <t>SKU-DEMO-DELI-003</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Snacks</t>
+          <t>Deli</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>44.78</v>
+        <v>141.43</v>
       </c>
       <c r="E21" t="n">
-        <v>28.21</v>
+        <v>99</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2027-10-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Wooden Kitchen Utensil Set</t>
+          <t>Corn Flakes 500g</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SKU-DEMO-MEAT-001</t>
+          <t>SKU-DEMO-PANTRY-004</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Meat</t>
+          <t>Breakfast &amp; Pantry</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>153.31</v>
+        <v>190.53</v>
       </c>
       <c r="E22" t="n">
-        <v>111.92</v>
+        <v>123.84</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2027-10-02</t>
+          <t>2028-08-15</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pet Training Clicker</t>
+          <t>White Bread Loaf</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SKU-DEMO-HOUSEHOLD-002</t>
+          <t>SKU-DEMO-BAKERY-002</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Household Supplies</t>
+          <t>Bakery</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16.13</v>
+        <v>198.31</v>
       </c>
       <c r="E23" t="n">
-        <v>9.359999999999999</v>
+        <v>142.78</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2028-07-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pasta (Linguine)</t>
+          <t>Instant Coffee 200g</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SKU-DEMO-DAIRY-002</t>
+          <t>SKU-DEMO-COFFEE-001</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Coffee &amp; Tea</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>280.01</v>
+        <v>299.68</v>
       </c>
       <c r="E24" t="n">
-        <v>190.41</v>
+        <v>179.81</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2028-02-13</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Organic Black Bean Burger</t>
+          <t>Baby Food Jar 200g</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SKU-DEMO-MEAT-002</t>
+          <t>SKU-DEMO-BABY-002</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Meat</t>
+          <t>Baby Products</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>163.8</v>
+        <v>188.02</v>
       </c>
       <c r="E25" t="n">
-        <v>119.57</v>
+        <v>112.81</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2028-01-28</t>
+          <t>2027-12-05</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aeropress Coffee Maker</t>
+          <t>Baby Food Jar 200g</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PET-002</t>
+          <t>SKU-DEMO-BABY-003</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Baby Products</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>255.29</v>
+        <v>12.11</v>
       </c>
       <c r="E26" t="n">
-        <v>153.17</v>
+        <v>7.27</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2028-06-30</t>
+          <t>2027-09-26</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Travel Yoga Mat</t>
+          <t>Cat Toys Set</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SKU-DEMO-BABY-001</t>
+          <t>SKU-DEMO-PET-001</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Baby Products</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>50.47</v>
+        <v>30.85</v>
       </c>
       <c r="E27" t="n">
-        <v>30.28</v>
+        <v>18.51</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2028-07-13</t>
+          <t>2027-10-09</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Plant Pot Drip Trays</t>
+          <t>Cinnamon Rolls</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PANTRY-003</t>
+          <t>SKU-DEMO-BAKERY-003</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Breakfast &amp; Pantry</t>
+          <t>Bakery</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>35.09</v>
+        <v>276.41</v>
       </c>
       <c r="E28" t="n">
-        <v>22.81</v>
+        <v>199.02</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2028-06-02</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Relaxed Fit Henley Shirt</t>
+          <t>Cat Food Cans 6-Pack</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SKU-DEMO-FROZEN-003</t>
+          <t>SKU-DEMO-PET-002</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Frozen Food</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>67.70999999999999</v>
+        <v>105.65</v>
       </c>
       <c r="E29" t="n">
-        <v>45.37</v>
+        <v>63.39</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2028-02-14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LED Flashlight</t>
+          <t>Canned Corn 400g</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SKU-DEMO-CLEAN-001</t>
+          <t>SKU-DEMO-CANNED-002</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cleaning Supplies</t>
+          <t>Canned Goods &amp; Legumes</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>136.97</v>
+        <v>20.86</v>
       </c>
       <c r="E30" t="n">
-        <v>78.06999999999999</v>
+        <v>13.56</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2028-05-21</t>
+          <t>2028-01-27</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Balsamic Vinaigrette</t>
+          <t>Frozen Pizza</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SKU-DEMO-BABY-002</t>
+          <t>SKU-DEMO-FROZEN-001</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Baby Products</t>
+          <t>Frozen Food</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>19.59</v>
+        <v>44.6</v>
       </c>
       <c r="E31" t="n">
-        <v>11.75</v>
+        <v>29.88</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2028-04-26</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ginger Turmeric Latte Mix</t>
+          <t>Frozen French Fries 1kg</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SKU-DEMO-BEV-002</t>
+          <t>SKU-DEMO-FROZEN-002</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Frozen Food</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>95.09</v>
+        <v>141.43</v>
       </c>
       <c r="E32" t="n">
-        <v>58.96</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2028-04-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Insulated Lunch Box</t>
+          <t>White Bread Loaf</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SKU-DEMO-BEV-003</t>
+          <t>SKU-DEMO-BAKERY-004</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Bakery</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>234.9</v>
+        <v>187.68</v>
       </c>
       <c r="E33" t="n">
-        <v>145.64</v>
+        <v>135.13</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2027-10-05</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Organic Black Bean Burger</t>
+          <t>Ground Coffee 250g</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SKU-DEMO-BEV-004</t>
+          <t>SKU-DEMO-COFFEE-002</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Coffee &amp; Tea</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>177.63</v>
+        <v>285.61</v>
       </c>
       <c r="E34" t="n">
-        <v>110.13</v>
+        <v>171.37</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2028-03-26</t>
+          <t>2027-09-28</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Wi-Fi Enabled Smart Light Switch</t>
+          <t>Greek Yogurt 500g</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SKU-DEMO-HOUSEHOLD-003</t>
+          <t>SKU-DEMO-DAIRY-001</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Household Supplies</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>70.23</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>40.73</v>
+        <v>6.43</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2027-11-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Smoked Gouda Cheese</t>
+          <t>Butter 250g</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SKU-DEMO-COFFEE-002</t>
+          <t>SKU-DEMO-DAIRY-002</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Coffee &amp; Tea</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>215.94</v>
+        <v>237.54</v>
       </c>
       <c r="E36" t="n">
-        <v>129.56</v>
+        <v>161.53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2028-05-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Faux Leather Leggings</t>
+          <t>Canned Chickpeas 400g</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SKU-DEMO-SNACK-003</t>
+          <t>SKU-DEMO-CANNED-003</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Snacks</t>
+          <t>Canned Goods &amp; Legumes</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>266.12</v>
+        <v>166.77</v>
       </c>
       <c r="E37" t="n">
-        <v>167.66</v>
+        <v>108.4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2027-09-28</t>
+          <t>2028-07-22</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Safety Goggles</t>
+          <t>Glass Cleaner 500ml</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SKU-DEMO-COFFEE-003</t>
+          <t>SKU-DEMO-CLEAN-002</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Coffee &amp; Tea</t>
+          <t>Cleaning Supplies</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>177</v>
+        <v>284.76</v>
       </c>
       <c r="E38" t="n">
-        <v>106.2</v>
+        <v>162.31</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2027-09-07</t>
+          <t>2027-09-25</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Whole Wheat Bread</t>
+          <t>Baby Food Jar 200g</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PERSCARE-002</t>
+          <t>SKU-DEMO-BABY-004</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Personal Care</t>
+          <t>Baby Products</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>242.46</v>
+        <v>56.18</v>
       </c>
       <c r="E39" t="n">
-        <v>133.35</v>
+        <v>33.71</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2027-09-21</t>
+          <t>2028-01-30</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Garlic Butter Shrimp</t>
+          <t>Beef Steak 400g</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PRODUCE-002</t>
+          <t>SKU-DEMO-MEAT-003</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Meat</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>154.55</v>
+        <v>189.68</v>
       </c>
       <c r="E40" t="n">
-        <v>115.91</v>
+        <v>138.47</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2027-09-13</t>
+          <t>2028-06-18</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pet Hair Vacuum Attachment</t>
+          <t>Cola 1.5L</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SKU-DEMO-FROZEN-004</t>
+          <t>SKU-DEMO-BEV-003</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Frozen Food</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>206.88</v>
+        <v>176.8</v>
       </c>
       <c r="E41" t="n">
-        <v>138.61</v>
+        <v>109.62</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2028-04-06</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Vegetable Spiralizer</t>
+          <t>Canned Chickpeas 400g</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SKU-DEMO-BABY-003</t>
+          <t>SKU-DEMO-CANNED-004</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Baby Products</t>
+          <t>Canned Goods &amp; Legumes</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>146.18</v>
+        <v>206.68</v>
       </c>
       <c r="E42" t="n">
-        <v>87.70999999999999</v>
+        <v>134.34</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2027-10-02</t>
+          <t>2028-05-23</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Dark Chocolate Tart</t>
+          <t>Baby Wipes Pack</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PANTRY-004</t>
+          <t>SKU-DEMO-BABY-005</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Breakfast &amp; Pantry</t>
+          <t>Baby Products</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>43.81</v>
+        <v>171.38</v>
       </c>
       <c r="E43" t="n">
-        <v>28.48</v>
+        <v>102.83</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2027-11-06</t>
+          <t>2027-10-29</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Children's Backpack</t>
+          <t>Frozen Pizza</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SKU-DEMO-CLEAN-002</t>
+          <t>SKU-DEMO-FROZEN-003</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cleaning Supplies</t>
+          <t>Frozen Food</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>23.19</v>
+        <v>228.45</v>
       </c>
       <c r="E44" t="n">
-        <v>13.22</v>
+        <v>153.06</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2028-01-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Foldable Picnic Table</t>
+          <t>Sliced Turkey Breast 200g</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SKU-DEMO-DELI-005</t>
+          <t>SKU-DEMO-DELI-004</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1669,194 +1669,194 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>155.36</v>
+        <v>206.65</v>
       </c>
       <c r="E45" t="n">
-        <v>108.75</v>
+        <v>144.66</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Almond Flour</t>
+          <t>Popcorn 100g</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PERSCARE-003</t>
+          <t>SKU-DEMO-SNACK-004</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Personal Care</t>
+          <t>Snacks</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>66.01000000000001</v>
+        <v>173.59</v>
       </c>
       <c r="E46" t="n">
-        <v>36.31</v>
+        <v>109.36</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2027-12-11</t>
+          <t>2027-12-28</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Italian Pasta</t>
+          <t>Bananas 1kg</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SKU-DEMO-COFFEE-004</t>
+          <t>SKU-DEMO-PRODUCE-002</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Coffee &amp; Tea</t>
+          <t>Produce</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>85.23</v>
+        <v>225.65</v>
       </c>
       <c r="E47" t="n">
-        <v>51.14</v>
+        <v>169.24</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2028-04-09</t>
+          <t>2027-11-18</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sea Salt Tortilla Chips</t>
+          <t>Pretzels 200g</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SKU-DEMO-DELI-006</t>
+          <t>SKU-DEMO-SNACK-005</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Deli</t>
+          <t>Snacks</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>265.22</v>
+        <v>24.65</v>
       </c>
       <c r="E48" t="n">
-        <v>185.65</v>
+        <v>15.53</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2028-08-17</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Eggs (dozen)</t>
+          <t>Butter 250g</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SKU-DEMO-CANNED-002</t>
+          <t>SKU-DEMO-DAIRY-003</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Canned Goods &amp; Legumes</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>238.1</v>
+        <v>121.42</v>
       </c>
       <c r="E49" t="n">
-        <v>154.77</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2028-03-11</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Spiralizer</t>
+          <t>Peanut Butter 400g</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PET-003</t>
+          <t>SKU-DEMO-PANTRY-005</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Breakfast &amp; Pantry</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>225.43</v>
+        <v>142.84</v>
       </c>
       <c r="E50" t="n">
-        <v>135.26</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2028-04-10</t>
+          <t>2027-08-21</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Baked Potato Chips</t>
+          <t>Cat Food Cans 6-Pack</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PRODUCE-003</t>
+          <t>SKU-DEMO-PET-003</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>285.54</v>
+        <v>13.37</v>
       </c>
       <c r="E51" t="n">
-        <v>214.16</v>
+        <v>8.02</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2028-07-27</t>
+          <t>2028-04-18</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ginger Tea</t>
+          <t>Red Apples 1kg</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PRODUCE-004</t>
+          <t>SKU-DEMO-PRODUCE-003</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1865,138 +1865,138 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>155.12</v>
+        <v>13.58</v>
       </c>
       <c r="E52" t="n">
-        <v>116.34</v>
+        <v>10.19</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2028-02-13</t>
+          <t>2027-08-19</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Blackberry Compote</t>
+          <t>Frozen Peas 500g</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SKU-DEMO-CANNED-003</t>
+          <t>SKU-DEMO-FROZEN-004</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Canned Goods &amp; Legumes</t>
+          <t>Frozen Food</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>91.86</v>
+        <v>250.74</v>
       </c>
       <c r="E53" t="n">
-        <v>59.71</v>
+        <v>168</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2027-12-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Spicy Salsa Verde</t>
+          <t>Sparkling Water 500ml</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PERSCARE-004</t>
+          <t>SKU-DEMO-BEV-004</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Personal Care</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>9.359999999999999</v>
+        <v>285.72</v>
       </c>
       <c r="E54" t="n">
-        <v>5.15</v>
+        <v>177.15</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2028-01-07</t>
+          <t>2027-11-25</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Luxury Bath Robe</t>
+          <t>Baby Food Jar 200g</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SKU-DEMO-SNACK-004</t>
+          <t>SKU-DEMO-BABY-006</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Snacks</t>
+          <t>Baby Products</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>271.25</v>
+        <v>115.82</v>
       </c>
       <c r="E55" t="n">
-        <v>170.89</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2028-08-07</t>
+          <t>2027-11-16</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Portable Pet Water Bottle</t>
+          <t>Cat Litter 5kg</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SKU-DEMO-MEAT-003</t>
+          <t>SKU-DEMO-PET-004</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Meat</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>183.3</v>
+        <v>27.07</v>
       </c>
       <c r="E56" t="n">
-        <v>133.81</v>
+        <v>16.24</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2028-01-16</t>
+          <t>2027-09-16</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Noise Reduction Headphones</t>
+          <t>Canned Tomatoes 400g</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SKU-DEMO-CANNED-004</t>
+          <t>SKU-DEMO-CANNED-005</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2005,245 +2005,245 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>33.79</v>
+        <v>264.88</v>
       </c>
       <c r="E57" t="n">
-        <v>21.96</v>
+        <v>172.17</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2027-10-31</t>
+          <t>2027-12-14</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Pumpkin Spice Creamer</t>
+          <t>Trash Bags 30ct</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SKU-DEMO-CLEAN-003</t>
+          <t>SKU-DEMO-HOUSEHOLD-002</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cleaning Supplies</t>
+          <t>Household Supplies</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>188.62</v>
+        <v>288.65</v>
       </c>
       <c r="E58" t="n">
-        <v>107.51</v>
+        <v>167.42</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2028-07-26</t>
+          <t>2027-11-15</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Elderberry Syrup Kit</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SKU-DEMO-DAIRY-003</t>
+          <t>SKU-DEMO-BAKERY-005</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Bakery</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>284.93</v>
+        <v>259.32</v>
       </c>
       <c r="E59" t="n">
-        <v>193.75</v>
+        <v>186.71</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Outdoor Picnic Blanket</t>
+          <t>Cat Toys Set</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SKU-DEMO-HOUSEHOLD-004</t>
+          <t>SKU-DEMO-PET-005</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Household Supplies</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>220.38</v>
+        <v>29.2</v>
       </c>
       <c r="E60" t="n">
-        <v>127.82</v>
+        <v>17.52</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2028-02-29</t>
+          <t>2028-04-08</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Coconut Oil</t>
+          <t>Bananas 1kg</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SKU-DEMO-COFFEE-005</t>
+          <t>SKU-DEMO-PRODUCE-004</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Coffee &amp; Tea</t>
+          <t>Produce</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>291.64</v>
+        <v>58.59</v>
       </c>
       <c r="E61" t="n">
-        <v>174.98</v>
+        <v>43.94</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2027-11-29</t>
+          <t>2028-02-13</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Savory Oatmeal</t>
+          <t>Beef Steak 400g</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SKU-DEMO-HOUSEHOLD-005</t>
+          <t>SKU-DEMO-MEAT-004</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Household Supplies</t>
+          <t>Meat</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>286.27</v>
+        <v>242</v>
       </c>
       <c r="E62" t="n">
-        <v>166.04</v>
+        <v>176.66</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2028-07-27</t>
+          <t>2028-05-11</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Wall Planner</t>
+          <t>Cheddar Cheese 400g</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SKU-DEMO-CANNED-005</t>
+          <t>SKU-DEMO-DAIRY-004</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Canned Goods &amp; Legumes</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>84.81999999999999</v>
+        <v>68.69</v>
       </c>
       <c r="E63" t="n">
-        <v>55.13</v>
+        <v>46.71</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2027-10-13</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Hiking Water Bottle with Filter</t>
+          <t>Toothpaste 100ml</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SKU-DEMO-BABY-004</t>
+          <t>SKU-DEMO-PERSCARE-002</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Baby Products</t>
+          <t>Personal Care</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>149.21</v>
+        <v>98.59</v>
       </c>
       <c r="E64" t="n">
-        <v>89.53</v>
+        <v>54.22</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2027-12-23</t>
+          <t>2028-02-27</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Solar Garden Lights</t>
+          <t>Dry Dog Food 2kg</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SKU-DEMO-SNACK-005</t>
+          <t>SKU-DEMO-PET-006</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Snacks</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>261.32</v>
+        <v>53.78</v>
       </c>
       <c r="E65" t="n">
-        <v>164.63</v>
+        <v>32.27</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2027-08-31</t>
+          <t>2028-05-27</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Silicone Baking Mat</t>
+          <t>Vanilla Ice Cream 1L</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2257,614 +2257,614 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>154.74</v>
+        <v>12.82</v>
       </c>
       <c r="E66" t="n">
-        <v>103.68</v>
+        <v>8.59</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Peach Preserves</t>
+          <t>Apple Juice 1L</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SKU-DEMO-SNACK-006</t>
+          <t>SKU-DEMO-BEV-005</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Snacks</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>32.5</v>
+        <v>45.23</v>
       </c>
       <c r="E67" t="n">
-        <v>20.48</v>
+        <v>28.04</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2028-04-25</t>
+          <t>2028-02-12</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Compost Bin</t>
+          <t>Ground Coffee 250g</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PET-004</t>
+          <t>SKU-DEMO-COFFEE-003</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Coffee &amp; Tea</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>113.19</v>
+        <v>108.58</v>
       </c>
       <c r="E68" t="n">
-        <v>67.91</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2028-01-09</t>
+          <t>2028-01-22</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Teriyaki Sauce</t>
+          <t>Black Tea Box 100ct</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SKU-DEMO-BEV-005</t>
+          <t>SKU-DEMO-COFFEE-004</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Coffee &amp; Tea</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>174.4</v>
+        <v>246.33</v>
       </c>
       <c r="E69" t="n">
-        <v>108.13</v>
+        <v>147.8</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2028-03-23</t>
+          <t>2027-10-26</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Popcorn Chicken</t>
+          <t>Black Tea Box 100ct</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SKU-DEMO-BAKERY-003</t>
+          <t>SKU-DEMO-COFFEE-005</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bakery</t>
+          <t>Coffee &amp; Tea</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>87.43000000000001</v>
+        <v>247.35</v>
       </c>
       <c r="E70" t="n">
-        <v>62.95</v>
+        <v>148.41</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-11-12</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sliced Olives</t>
+          <t>Whole Wheat Bread</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PET-005</t>
+          <t>SKU-DEMO-BAKERY-006</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Bakery</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>88.84999999999999</v>
+        <v>149.31</v>
       </c>
       <c r="E71" t="n">
-        <v>53.31</v>
+        <v>107.5</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2028-02-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Pesto Genovese</t>
+          <t>Pork Chops 500g</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PERSCARE-005</t>
+          <t>SKU-DEMO-MEAT-005</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Personal Care</t>
+          <t>Meat</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>195.99</v>
+        <v>274.44</v>
       </c>
       <c r="E72" t="n">
-        <v>107.79</v>
+        <v>200.34</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2027-11-24</t>
+          <t>2028-07-31</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Italian Herbal Seasoning</t>
+          <t>Trash Bags 30ct</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SKU-DEMO-DAIRY-004</t>
+          <t>SKU-DEMO-HOUSEHOLD-003</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Household Supplies</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>184.81</v>
+        <v>96.12</v>
       </c>
       <c r="E73" t="n">
-        <v>125.67</v>
+        <v>55.75</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2028-03-15</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Pet Reflective Vest</t>
+          <t>Prosciutto 100g</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SKU-DEMO-HOUSEHOLD-006</t>
+          <t>SKU-DEMO-DELI-005</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Household Supplies</t>
+          <t>Deli</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>95.92</v>
+        <v>275.05</v>
       </c>
       <c r="E74" t="n">
-        <v>55.63</v>
+        <v>192.53</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2028-08-08</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Savory Trail Mix</t>
+          <t>Green Olives 400g</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SKU-DEMO-MEAT-004</t>
+          <t>SKU-DEMO-DELI-006</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Meat</t>
+          <t>Deli</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>138.43</v>
+        <v>204.04</v>
       </c>
       <c r="E75" t="n">
-        <v>101.05</v>
+        <v>142.83</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2028-03-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>LED Strip Lights</t>
+          <t>Dish Soap 750ml</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SKU-DEMO-BABY-005</t>
+          <t>SKU-DEMO-CLEAN-003</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Baby Products</t>
+          <t>Cleaning Supplies</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>244.32</v>
+        <v>14.18</v>
       </c>
       <c r="E76" t="n">
-        <v>146.59</v>
+        <v>8.08</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2027-09-01</t>
+          <t>2028-01-19</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sliced Turkey Breast</t>
+          <t>Aluminum Foil Roll</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PANTRY-005</t>
+          <t>SKU-DEMO-HOUSEHOLD-004</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Breakfast &amp; Pantry</t>
+          <t>Household Supplies</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>195.61</v>
+        <v>232.52</v>
       </c>
       <c r="E77" t="n">
-        <v>127.15</v>
+        <v>134.86</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2027-11-18</t>
+          <t>2027-09-06</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Rice Noodles</t>
+          <t>Heavy Cream 200ml</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PERSCARE-006</t>
+          <t>SKU-DEMO-DAIRY-005</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Personal Care</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>95.78</v>
+        <v>215.79</v>
       </c>
       <c r="E78" t="n">
-        <v>52.68</v>
+        <v>146.74</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2028-07-08</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Corn Tortillas</t>
+          <t>Bananas 1kg</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PET-006</t>
+          <t>SKU-DEMO-PRODUCE-005</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Produce</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>199.23</v>
+        <v>248.86</v>
       </c>
       <c r="E79" t="n">
-        <v>119.54</v>
+        <v>186.65</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2028-01-14</t>
+          <t>2028-08-09</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Coconut Curry Lentils</t>
+          <t>Aluminum Foil Roll</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SKU-DEMO-CLEAN-004</t>
+          <t>SKU-DEMO-HOUSEHOLD-005</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cleaning Supplies</t>
+          <t>Household Supplies</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>205.67</v>
+        <v>173.56</v>
       </c>
       <c r="E80" t="n">
-        <v>117.23</v>
+        <v>100.66</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2028-02-04</t>
+          <t>2028-07-10</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Fitness Jump Rope with LCD Counter</t>
+          <t>Sliced Turkey Breast 200g</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SKU-DEMO-CANNED-006</t>
+          <t>SKU-DEMO-DELI-007</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Canned Goods &amp; Legumes</t>
+          <t>Deli</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>224.27</v>
+        <v>122.21</v>
       </c>
       <c r="E81" t="n">
-        <v>145.78</v>
+        <v>85.55</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2028-01-24</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Rustic Wooden Picture Frame</t>
+          <t>Orange Juice 1L</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SKU-DEMO-BAKERY-004</t>
+          <t>SKU-DEMO-BEV-006</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bakery</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>210.01</v>
+        <v>119.84</v>
       </c>
       <c r="E82" t="n">
-        <v>151.21</v>
+        <v>74.3</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2027-09-03</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>LED Desk Light</t>
+          <t>Greek Yogurt 500g</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PRODUCE-005</t>
+          <t>SKU-DEMO-DAIRY-006</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>207.6</v>
+        <v>21.8</v>
       </c>
       <c r="E83" t="n">
-        <v>155.7</v>
+        <v>14.82</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2027-09-30</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Car Emergency Kit</t>
+          <t>Toothpaste 100ml</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SKU-DEMO-COFFEE-006</t>
+          <t>SKU-DEMO-PERSCARE-003</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Coffee &amp; Tea</t>
+          <t>Personal Care</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>9.85</v>
+        <v>233.47</v>
       </c>
       <c r="E84" t="n">
-        <v>5.91</v>
+        <v>128.41</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2028-02-12</t>
+          <t>2028-02-22</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Caramel Apple Taffy</t>
+          <t>Deodorant 150ml</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SKU-DEMO-FROZEN-006</t>
+          <t>SKU-DEMO-PERSCARE-004</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Frozen Food</t>
+          <t>Personal Care</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>108.84</v>
+        <v>132.56</v>
       </c>
       <c r="E85" t="n">
-        <v>72.92</v>
+        <v>72.91</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2027-09-08</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Organic Black Rice</t>
+          <t>Coffee Pods 12-Pack</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SKU-DEMO-DELI-007</t>
+          <t>SKU-DEMO-COFFEE-006</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Deli</t>
+          <t>Coffee &amp; Tea</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>286.55</v>
+        <v>217.4</v>
       </c>
       <c r="E86" t="n">
-        <v>200.59</v>
+        <v>130.44</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2028-06-14</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Peach Slices in Syrup</t>
+          <t>Paper Towels 4-Pack</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PANTRY-006</t>
+          <t>SKU-DEMO-HOUSEHOLD-006</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Breakfast &amp; Pantry</t>
+          <t>Household Supplies</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>19.12</v>
+        <v>20.53</v>
       </c>
       <c r="E87" t="n">
-        <v>12.43</v>
+        <v>11.91</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2027-11-22</t>
+          <t>2027-10-12</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Children's Educational Workbook</t>
+          <t>Vanilla Ice Cream 1L</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SKU-DEMO-FROZEN-007</t>
+          <t>SKU-DEMO-FROZEN-006</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2873,194 +2873,194 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>289.94</v>
+        <v>25.51</v>
       </c>
       <c r="E88" t="n">
-        <v>194.26</v>
+        <v>17.09</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Outdoor Picnic Blanket</t>
+          <t>Spaghetti 500g</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SKU-DEMO-MEAT-005</t>
+          <t>SKU-DEMO-PANTRY-006</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Meat</t>
+          <t>Breakfast &amp; Pantry</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>265.56</v>
+        <v>107.69</v>
       </c>
       <c r="E89" t="n">
-        <v>193.86</v>
+        <v>70</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2027-12-25</t>
+          <t>2028-05-23</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Foam Muscle Roller</t>
+          <t>Dish Soap 750ml</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SKU-DEMO-BAKERY-005</t>
+          <t>SKU-DEMO-CLEAN-004</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bakery</t>
+          <t>Cleaning Supplies</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>214.93</v>
+        <v>215.01</v>
       </c>
       <c r="E90" t="n">
-        <v>154.75</v>
+        <v>122.56</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2028-03-15</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Herb Seasoned Rice</t>
+          <t>Glass Cleaner 500ml</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SKU-DEMO-BABY-006</t>
+          <t>SKU-DEMO-CLEAN-005</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Baby Products</t>
+          <t>Cleaning Supplies</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>254.46</v>
+        <v>114.34</v>
       </c>
       <c r="E91" t="n">
-        <v>152.68</v>
+        <v>65.17</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2028-08-01</t>
+          <t>2028-02-06</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Desk Lamp with USB Port</t>
+          <t>Bleach 1L</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SKU-DEMO-BAKERY-006</t>
+          <t>SKU-DEMO-CLEAN-006</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bakery</t>
+          <t>Cleaning Supplies</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>136.31</v>
+        <v>179.48</v>
       </c>
       <c r="E92" t="n">
-        <v>98.14</v>
+        <v>102.3</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2028-02-20</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Bamboo Utensil Holder</t>
+          <t>Shampoo 400ml</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SKU-DEMO-BEV-006</t>
+          <t>SKU-DEMO-PERSCARE-005</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Personal Care</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>102.07</v>
+        <v>263.23</v>
       </c>
       <c r="E93" t="n">
-        <v>63.28</v>
+        <v>144.78</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2028-01-08</t>
+          <t>2028-06-23</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Chocolate Chip Pancake Mix</t>
+          <t>Hand Soap 300ml</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SKU-DEMO-CLEAN-005</t>
+          <t>SKU-DEMO-PERSCARE-006</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cleaning Supplies</t>
+          <t>Personal Care</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>114.17</v>
+        <v>212.33</v>
       </c>
       <c r="E94" t="n">
-        <v>65.08</v>
+        <v>116.78</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2028-07-10</t>
+          <t>2028-05-02</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sliced Bread</t>
+          <t>Butter 250g</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SKU-DEMO-DAIRY-005</t>
+          <t>SKU-DEMO-DAIRY-007</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3069,182 +3069,182 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>231.15</v>
+        <v>128.03</v>
       </c>
       <c r="E95" t="n">
-        <v>157.18</v>
+        <v>87.06</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Car Emergency Kit</t>
+          <t>Carrots 1kg</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SKU-DEMO-BAKERY-007</t>
+          <t>SKU-DEMO-PRODUCE-006</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bakery</t>
+          <t>Produce</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12.61</v>
+        <v>56.43</v>
       </c>
       <c r="E96" t="n">
-        <v>9.08</v>
+        <v>42.32</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2027-10-12</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Digital Photo Frame</t>
+          <t>Vanilla Ice Cream 1L</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SKU-DEMO-MEAT-006</t>
+          <t>SKU-DEMO-FROZEN-007</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Meat</t>
+          <t>Frozen Food</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>122.86</v>
+        <v>257.91</v>
       </c>
       <c r="E97" t="n">
-        <v>89.69</v>
+        <v>172.8</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2028-08-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Canvas High-Top Sneakers</t>
+          <t>Potato Chips 150g</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SKU-DEMO-DAIRY-006</t>
+          <t>SKU-DEMO-SNACK-006</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Snacks</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>94.08</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="E98" t="n">
-        <v>63.97</v>
+        <v>40.79</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2027-10-12</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Multi-Functional Rice Cooker</t>
+          <t>Pork Chops 500g</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SKU-DEMO-DAIRY-007</t>
+          <t>SKU-DEMO-MEAT-006</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Meat</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>290.67</v>
+        <v>285.97</v>
       </c>
       <c r="E99" t="n">
-        <v>197.66</v>
+        <v>208.76</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2028-01-29</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Stainless Steel Grater</t>
+          <t>Canned Chickpeas 400g</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SKU-DEMO-PRODUCE-006</t>
+          <t>SKU-DEMO-CANNED-006</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Canned Goods &amp; Legumes</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>203.03</v>
+        <v>291.68</v>
       </c>
       <c r="E100" t="n">
-        <v>152.27</v>
+        <v>189.59</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2027-12-01</t>
+          <t>2027-11-02</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Pet Training Clicker</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SKU-DEMO-CLEAN-006</t>
+          <t>SKU-DEMO-BAKERY-007</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cleaning Supplies</t>
+          <t>Bakery</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>68.64</v>
+        <v>264.98</v>
       </c>
       <c r="E101" t="n">
-        <v>39.12</v>
+        <v>190.79</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2028-04-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
